--- a/templates/Trial Balance_template.xlsx
+++ b/templates/Trial Balance_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardpalenik/Dropbox/python-development/GenAI/ecos/trial_balance/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA0C9C2-7A47-1F47-9596-F9A32E5A8C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55172CB2-1A30-AE4C-AC52-11152B0A5557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="1935">
   <si>
     <t>sal_konto</t>
   </si>
@@ -5825,6 +5825,9 @@
   </si>
   <si>
     <t>472100</t>
+  </si>
+  <si>
+    <t>511990</t>
   </si>
 </sst>
 </file>
@@ -6188,7 +6191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S663"/>
+  <dimension ref="A1:S664"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.5" style="9" bestFit="1" customWidth="1"/>
@@ -23251,13 +23254,13 @@
     </row>
     <row r="424" spans="1:12" ht="15">
       <c r="A424" s="8" t="s">
-        <v>742</v>
+        <v>1934</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1253</v>
+        <v>243</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1750</v>
+        <v>244</v>
       </c>
       <c r="D424" s="2">
         <v>202301</v>
@@ -23289,13 +23292,13 @@
     </row>
     <row r="425" spans="1:12" ht="15">
       <c r="A425" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="D425" s="2">
         <v>202301</v>
@@ -23327,13 +23330,13 @@
     </row>
     <row r="426" spans="1:12" ht="15">
       <c r="A426" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="D426" s="2">
         <v>202301</v>
@@ -23365,13 +23368,13 @@
     </row>
     <row r="427" spans="1:12" ht="15">
       <c r="A427" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="D427" s="2">
         <v>202301</v>
@@ -23403,13 +23406,13 @@
     </row>
     <row r="428" spans="1:12" ht="15">
       <c r="A428" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D428" s="2">
         <v>202301</v>
@@ -23441,13 +23444,13 @@
     </row>
     <row r="429" spans="1:12" ht="15">
       <c r="A429" s="8" t="s">
-        <v>248</v>
+        <v>746</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>249</v>
+        <v>1257</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>250</v>
+        <v>1754</v>
       </c>
       <c r="D429" s="2">
         <v>202301</v>
@@ -23479,13 +23482,13 @@
     </row>
     <row r="430" spans="1:12" ht="15">
       <c r="A430" s="8" t="s">
-        <v>747</v>
+        <v>248</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1258</v>
+        <v>249</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1755</v>
+        <v>250</v>
       </c>
       <c r="D430" s="2">
         <v>202301</v>
@@ -23517,13 +23520,13 @@
     </row>
     <row r="431" spans="1:12" ht="15">
       <c r="A431" s="8" t="s">
-        <v>251</v>
+        <v>747</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>252</v>
+        <v>1258</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>253</v>
+        <v>1755</v>
       </c>
       <c r="D431" s="2">
         <v>202301</v>
@@ -23555,13 +23558,13 @@
     </row>
     <row r="432" spans="1:12" ht="15">
       <c r="A432" s="8" t="s">
-        <v>748</v>
+        <v>251</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>252</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1756</v>
+        <v>253</v>
       </c>
       <c r="D432" s="2">
         <v>202301</v>
@@ -23593,13 +23596,13 @@
     </row>
     <row r="433" spans="1:12" ht="15">
       <c r="A433" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1259</v>
+        <v>252</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D433" s="2">
         <v>202301</v>
@@ -23631,13 +23634,13 @@
     </row>
     <row r="434" spans="1:12" ht="15">
       <c r="A434" s="8" t="s">
-        <v>254</v>
+        <v>749</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>255</v>
+        <v>1259</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>256</v>
+        <v>1757</v>
       </c>
       <c r="D434" s="2">
         <v>202301</v>
@@ -23669,13 +23672,13 @@
     </row>
     <row r="435" spans="1:12" ht="15">
       <c r="A435" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D435" s="2">
         <v>202301</v>
@@ -23707,13 +23710,13 @@
     </row>
     <row r="436" spans="1:12" ht="15">
       <c r="A436" s="8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D436" s="2">
         <v>202301</v>
@@ -23745,13 +23748,13 @@
     </row>
     <row r="437" spans="1:12" ht="15">
       <c r="A437" s="8" t="s">
-        <v>750</v>
+        <v>260</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1260</v>
+        <v>261</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1758</v>
+        <v>262</v>
       </c>
       <c r="D437" s="2">
         <v>202301</v>
@@ -23783,13 +23786,13 @@
     </row>
     <row r="438" spans="1:12" ht="15">
       <c r="A438" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D438" s="2">
         <v>202301</v>
@@ -23821,13 +23824,13 @@
     </row>
     <row r="439" spans="1:12" ht="15">
       <c r="A439" s="8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="D439" s="2">
         <v>202301</v>
@@ -23859,13 +23862,13 @@
     </row>
     <row r="440" spans="1:12" ht="15">
       <c r="A440" s="8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="D440" s="2">
         <v>202301</v>
@@ -23897,13 +23900,13 @@
     </row>
     <row r="441" spans="1:12" ht="15">
       <c r="A441" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="D441" s="2">
         <v>202301</v>
@@ -23935,13 +23938,13 @@
     </row>
     <row r="442" spans="1:12" ht="15">
       <c r="A442" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="D442" s="2">
         <v>202301</v>
@@ -23973,13 +23976,13 @@
     </row>
     <row r="443" spans="1:12" ht="15">
       <c r="A443" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1266</v>
+        <v>1763</v>
       </c>
       <c r="D443" s="2">
         <v>202301</v>
@@ -24011,13 +24014,13 @@
     </row>
     <row r="444" spans="1:12" ht="15">
       <c r="A444" s="8" t="s">
-        <v>263</v>
+        <v>756</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>264</v>
+        <v>1266</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>265</v>
+        <v>1266</v>
       </c>
       <c r="D444" s="2">
         <v>202301</v>
@@ -24049,13 +24052,13 @@
     </row>
     <row r="445" spans="1:12" ht="15">
       <c r="A445" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D445" s="2">
         <v>202301</v>
@@ -24087,13 +24090,13 @@
     </row>
     <row r="446" spans="1:12" ht="15">
       <c r="A446" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D446" s="2">
         <v>202301</v>
@@ -24125,13 +24128,13 @@
     </row>
     <row r="447" spans="1:12" ht="15">
       <c r="A447" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D447" s="2">
         <v>202301</v>
@@ -24163,13 +24166,13 @@
     </row>
     <row r="448" spans="1:12" ht="15">
       <c r="A448" s="8" t="s">
-        <v>757</v>
+        <v>272</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>1267</v>
+        <v>273</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1764</v>
+        <v>274</v>
       </c>
       <c r="D448" s="2">
         <v>202301</v>
@@ -24201,13 +24204,13 @@
     </row>
     <row r="449" spans="1:12" ht="15">
       <c r="A449" s="8" t="s">
-        <v>275</v>
+        <v>757</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>258</v>
+        <v>1267</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>259</v>
+        <v>1764</v>
       </c>
       <c r="D449" s="2">
         <v>202301</v>
@@ -24239,13 +24242,13 @@
     </row>
     <row r="450" spans="1:12" ht="15">
       <c r="A450" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="D450" s="2">
         <v>202301</v>
@@ -24277,13 +24280,13 @@
     </row>
     <row r="451" spans="1:12" ht="15">
       <c r="A451" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D451" s="2">
         <v>202301</v>
@@ -24315,13 +24318,13 @@
     </row>
     <row r="452" spans="1:12" ht="15">
       <c r="A452" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D452" s="2">
         <v>202301</v>
@@ -24353,13 +24356,13 @@
     </row>
     <row r="453" spans="1:12" ht="15">
       <c r="A453" s="8" t="s">
-        <v>758</v>
+        <v>282</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1268</v>
+        <v>283</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1765</v>
+        <v>284</v>
       </c>
       <c r="D453" s="2">
         <v>202301</v>
@@ -24391,13 +24394,13 @@
     </row>
     <row r="454" spans="1:12" ht="15">
       <c r="A454" s="8" t="s">
-        <v>285</v>
+        <v>758</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>286</v>
+        <v>1268</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>287</v>
+        <v>1765</v>
       </c>
       <c r="D454" s="2">
         <v>202301</v>
@@ -24429,13 +24432,13 @@
     </row>
     <row r="455" spans="1:12" ht="15">
       <c r="A455" s="8" t="s">
-        <v>759</v>
+        <v>285</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1269</v>
+        <v>286</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1766</v>
+        <v>287</v>
       </c>
       <c r="D455" s="2">
         <v>202301</v>
@@ -24467,13 +24470,13 @@
     </row>
     <row r="456" spans="1:12" ht="15">
       <c r="A456" s="8" t="s">
-        <v>288</v>
+        <v>759</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>289</v>
+        <v>1269</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>290</v>
+        <v>1766</v>
       </c>
       <c r="D456" s="2">
         <v>202301</v>
@@ -24505,13 +24508,13 @@
     </row>
     <row r="457" spans="1:12" ht="15">
       <c r="A457" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D457" s="2">
         <v>202301</v>
@@ -24543,13 +24546,13 @@
     </row>
     <row r="458" spans="1:12" ht="15">
       <c r="A458" s="8" t="s">
-        <v>760</v>
+        <v>291</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>1270</v>
+        <v>292</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1767</v>
+        <v>293</v>
       </c>
       <c r="D458" s="2">
         <v>202301</v>
@@ -24581,13 +24584,13 @@
     </row>
     <row r="459" spans="1:12" ht="15">
       <c r="A459" s="8" t="s">
-        <v>294</v>
+        <v>760</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>295</v>
+        <v>1270</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>296</v>
+        <v>1767</v>
       </c>
       <c r="D459" s="2">
         <v>202301</v>
@@ -24619,13 +24622,13 @@
     </row>
     <row r="460" spans="1:12" ht="15">
       <c r="A460" s="8" t="s">
-        <v>761</v>
+        <v>294</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1271</v>
+        <v>295</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1768</v>
+        <v>296</v>
       </c>
       <c r="D460" s="2">
         <v>202301</v>
@@ -24657,13 +24660,13 @@
     </row>
     <row r="461" spans="1:12" ht="15">
       <c r="A461" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="D461" s="2">
         <v>202301</v>
@@ -24695,13 +24698,13 @@
     </row>
     <row r="462" spans="1:12" ht="15">
       <c r="A462" s="8" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="D462" s="2">
         <v>202301</v>
@@ -24733,13 +24736,13 @@
     </row>
     <row r="463" spans="1:12" ht="15">
       <c r="A463" s="8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="D463" s="2">
         <v>202301</v>
@@ -24771,13 +24774,13 @@
     </row>
     <row r="464" spans="1:12" ht="15">
       <c r="A464" s="8" t="s">
-        <v>297</v>
+        <v>764</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>273</v>
+        <v>1274</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>274</v>
+        <v>1771</v>
       </c>
       <c r="D464" s="2">
         <v>202301</v>
@@ -24809,13 +24812,13 @@
     </row>
     <row r="465" spans="1:12" ht="15">
       <c r="A465" s="8" t="s">
-        <v>765</v>
+        <v>297</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1275</v>
+        <v>273</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1772</v>
+        <v>274</v>
       </c>
       <c r="D465" s="2">
         <v>202301</v>
@@ -24847,13 +24850,13 @@
     </row>
     <row r="466" spans="1:12" ht="15">
       <c r="A466" s="8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D466" s="2">
         <v>202301</v>
@@ -24885,13 +24888,13 @@
     </row>
     <row r="467" spans="1:12" ht="15">
       <c r="A467" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="D467" s="2">
         <v>202301</v>
@@ -24923,13 +24926,13 @@
     </row>
     <row r="468" spans="1:12" ht="15">
       <c r="A468" s="8" t="s">
-        <v>298</v>
+        <v>767</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>299</v>
+        <v>1277</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>300</v>
+        <v>1774</v>
       </c>
       <c r="D468" s="2">
         <v>202301</v>
@@ -24961,13 +24964,13 @@
     </row>
     <row r="469" spans="1:12" ht="15">
       <c r="A469" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D469" s="2">
         <v>202301</v>
@@ -24999,13 +25002,13 @@
     </row>
     <row r="470" spans="1:12" ht="15">
       <c r="A470" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D470" s="2">
         <v>202301</v>
@@ -25037,13 +25040,13 @@
     </row>
     <row r="471" spans="1:12" ht="15">
       <c r="A471" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>307</v>
+        <v>401</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D471" s="2">
         <v>202301</v>
@@ -25075,13 +25078,13 @@
     </row>
     <row r="472" spans="1:12" ht="15">
       <c r="A472" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D472" s="2">
         <v>202301</v>
@@ -25113,13 +25116,13 @@
     </row>
     <row r="473" spans="1:12" ht="15">
       <c r="A473" s="8" t="s">
-        <v>768</v>
+        <v>309</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1278</v>
+        <v>310</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1775</v>
+        <v>311</v>
       </c>
       <c r="D473" s="2">
         <v>202301</v>
@@ -25151,13 +25154,13 @@
     </row>
     <row r="474" spans="1:12" ht="15">
       <c r="A474" s="8" t="s">
-        <v>312</v>
+        <v>768</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>307</v>
+        <v>1278</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>308</v>
+        <v>1775</v>
       </c>
       <c r="D474" s="2">
         <v>202301</v>
@@ -25189,13 +25192,13 @@
     </row>
     <row r="475" spans="1:12" ht="15">
       <c r="A475" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D475" s="2">
         <v>202301</v>
@@ -25227,13 +25230,13 @@
     </row>
     <row r="476" spans="1:12" ht="15">
       <c r="A476" s="8" t="s">
-        <v>769</v>
+        <v>313</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1279</v>
+        <v>314</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1776</v>
+        <v>315</v>
       </c>
       <c r="D476" s="2">
         <v>202301</v>
@@ -25265,13 +25268,13 @@
     </row>
     <row r="477" spans="1:12" ht="15">
       <c r="A477" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="D477" s="2">
         <v>202301</v>
@@ -25303,13 +25306,13 @@
     </row>
     <row r="478" spans="1:12" ht="15">
       <c r="A478" s="8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="D478" s="2">
         <v>202301</v>
@@ -25341,13 +25344,13 @@
     </row>
     <row r="479" spans="1:12" ht="15">
       <c r="A479" s="8" t="s">
-        <v>316</v>
+        <v>771</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>117</v>
+        <v>1281</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>317</v>
+        <v>1778</v>
       </c>
       <c r="D479" s="2">
         <v>202301</v>
@@ -25379,13 +25382,13 @@
     </row>
     <row r="480" spans="1:12" ht="15">
       <c r="A480" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D480" s="2">
         <v>202301</v>
@@ -25417,13 +25420,13 @@
     </row>
     <row r="481" spans="1:12" ht="15">
       <c r="A481" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>321</v>
+        <v>120</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D481" s="2">
         <v>202301</v>
@@ -25455,13 +25458,13 @@
     </row>
     <row r="482" spans="1:12" ht="15">
       <c r="A482" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>389</v>
+        <v>321</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D482" s="2">
         <v>202301</v>
@@ -25493,13 +25496,13 @@
     </row>
     <row r="483" spans="1:12" ht="15">
       <c r="A483" s="8" t="s">
-        <v>772</v>
+        <v>323</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1282</v>
+        <v>389</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1779</v>
+        <v>324</v>
       </c>
       <c r="D483" s="2">
         <v>202301</v>
@@ -25531,13 +25534,13 @@
     </row>
     <row r="484" spans="1:12" ht="15">
       <c r="A484" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="D484" s="2">
         <v>202301</v>
@@ -25569,13 +25572,13 @@
     </row>
     <row r="485" spans="1:12" ht="15">
       <c r="A485" s="8" t="s">
-        <v>325</v>
+        <v>773</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>326</v>
+        <v>1283</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>327</v>
+        <v>1780</v>
       </c>
       <c r="D485" s="2">
         <v>202301</v>
@@ -25607,13 +25610,13 @@
     </row>
     <row r="486" spans="1:12" ht="15">
       <c r="A486" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D486" s="2">
         <v>202301</v>
@@ -25645,13 +25648,13 @@
     </row>
     <row r="487" spans="1:12" ht="15">
       <c r="A487" s="8" t="s">
-        <v>774</v>
+        <v>328</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1284</v>
+        <v>329</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1781</v>
+        <v>330</v>
       </c>
       <c r="D487" s="2">
         <v>202301</v>
@@ -25683,13 +25686,13 @@
     </row>
     <row r="488" spans="1:12" ht="15">
       <c r="A488" s="8" t="s">
-        <v>331</v>
+        <v>774</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>332</v>
+        <v>1284</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>333</v>
+        <v>1781</v>
       </c>
       <c r="D488" s="2">
         <v>202301</v>
@@ -25721,13 +25724,13 @@
     </row>
     <row r="489" spans="1:12" ht="15">
       <c r="A489" s="8" t="s">
-        <v>775</v>
+        <v>331</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1285</v>
+        <v>332</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1782</v>
+        <v>333</v>
       </c>
       <c r="D489" s="2">
         <v>202301</v>
@@ -25759,13 +25762,13 @@
     </row>
     <row r="490" spans="1:12" ht="15">
       <c r="A490" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="D490" s="2">
         <v>202301</v>
@@ -25797,13 +25800,13 @@
     </row>
     <row r="491" spans="1:12" ht="15">
       <c r="A491" s="8" t="s">
-        <v>334</v>
+        <v>776</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>335</v>
+        <v>1286</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>336</v>
+        <v>1783</v>
       </c>
       <c r="D491" s="2">
         <v>202301</v>
@@ -25835,13 +25838,13 @@
     </row>
     <row r="492" spans="1:12" ht="15">
       <c r="A492" s="8" t="s">
-        <v>777</v>
+        <v>334</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1287</v>
+        <v>335</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1784</v>
+        <v>336</v>
       </c>
       <c r="D492" s="2">
         <v>202301</v>
@@ -25873,13 +25876,13 @@
     </row>
     <row r="493" spans="1:12" ht="15">
       <c r="A493" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="D493" s="2">
         <v>202301</v>
@@ -25911,13 +25914,13 @@
     </row>
     <row r="494" spans="1:12" ht="15">
       <c r="A494" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="D494" s="2">
         <v>202301</v>
@@ -25949,13 +25952,13 @@
     </row>
     <row r="495" spans="1:12" ht="15">
       <c r="A495" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="D495" s="2">
         <v>202301</v>
@@ -25987,13 +25990,13 @@
     </row>
     <row r="496" spans="1:12" ht="15">
       <c r="A496" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="D496" s="2">
         <v>202301</v>
@@ -26025,13 +26028,13 @@
     </row>
     <row r="497" spans="1:12" ht="15">
       <c r="A497" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="D497" s="2">
         <v>202301</v>
@@ -26063,13 +26066,13 @@
     </row>
     <row r="498" spans="1:12" ht="15">
       <c r="A498" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="D498" s="2">
         <v>202301</v>
@@ -26101,13 +26104,13 @@
     </row>
     <row r="499" spans="1:12" ht="15">
       <c r="A499" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="D499" s="2">
         <v>202301</v>
@@ -26139,13 +26142,13 @@
     </row>
     <row r="500" spans="1:12" ht="15">
       <c r="A500" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1114</v>
+        <v>1294</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1611</v>
+        <v>1791</v>
       </c>
       <c r="D500" s="2">
         <v>202301</v>
@@ -26177,13 +26180,13 @@
     </row>
     <row r="501" spans="1:12" ht="15">
       <c r="A501" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>144</v>
+        <v>1114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1792</v>
+        <v>1611</v>
       </c>
       <c r="D501" s="2">
         <v>202301</v>
@@ -26215,13 +26218,13 @@
     </row>
     <row r="502" spans="1:12" ht="15">
       <c r="A502" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1115</v>
+        <v>144</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1612</v>
+        <v>1792</v>
       </c>
       <c r="D502" s="2">
         <v>202301</v>
@@ -26253,13 +26256,13 @@
     </row>
     <row r="503" spans="1:12" ht="15">
       <c r="A503" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1295</v>
+        <v>1115</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D503" s="2">
         <v>202301</v>
@@ -26291,13 +26294,13 @@
     </row>
     <row r="504" spans="1:12" ht="15">
       <c r="A504" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1117</v>
+        <v>1295</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>1793</v>
+        <v>1613</v>
       </c>
       <c r="D504" s="2">
         <v>202301</v>
@@ -26329,13 +26332,13 @@
     </row>
     <row r="505" spans="1:12" ht="15">
       <c r="A505" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1296</v>
+        <v>1117</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="D505" s="2">
         <v>202301</v>
@@ -26367,13 +26370,13 @@
     </row>
     <row r="506" spans="1:12" ht="15">
       <c r="A506" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="D506" s="2">
         <v>202301</v>
@@ -26405,13 +26408,13 @@
     </row>
     <row r="507" spans="1:12" ht="15">
       <c r="A507" s="8" t="s">
-        <v>337</v>
+        <v>791</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>338</v>
+        <v>1297</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>339</v>
+        <v>1789</v>
       </c>
       <c r="D507" s="2">
         <v>202301</v>
@@ -26443,13 +26446,13 @@
     </row>
     <row r="508" spans="1:12" ht="15">
       <c r="A508" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>402</v>
+        <v>338</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D508" s="2">
         <v>202301</v>
@@ -26481,13 +26484,13 @@
     </row>
     <row r="509" spans="1:12" ht="15">
       <c r="A509" s="8" t="s">
-        <v>792</v>
+        <v>340</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1298</v>
+        <v>402</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1795</v>
+        <v>341</v>
       </c>
       <c r="D509" s="2">
         <v>202301</v>
@@ -26519,13 +26522,13 @@
     </row>
     <row r="510" spans="1:12" ht="15">
       <c r="A510" s="8" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="D510" s="2">
         <v>202301</v>
@@ -26557,13 +26560,13 @@
     </row>
     <row r="511" spans="1:12" ht="15">
       <c r="A511" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="D511" s="2">
         <v>202301</v>
@@ -26595,13 +26598,13 @@
     </row>
     <row r="512" spans="1:12" ht="15">
       <c r="A512" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="D512" s="2">
         <v>202301</v>
@@ -26633,13 +26636,13 @@
     </row>
     <row r="513" spans="1:12" ht="15">
       <c r="A513" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="D513" s="2">
         <v>202301</v>
@@ -26671,13 +26674,13 @@
     </row>
     <row r="514" spans="1:12" ht="15">
       <c r="A514" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="D514" s="2">
         <v>202301</v>
@@ -26709,13 +26712,13 @@
     </row>
     <row r="515" spans="1:12" ht="15">
       <c r="A515" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D515" s="2">
         <v>202301</v>
@@ -26747,13 +26750,13 @@
     </row>
     <row r="516" spans="1:12" ht="15">
       <c r="A516" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="D516" s="2">
         <v>202301</v>
@@ -26785,13 +26788,13 @@
     </row>
     <row r="517" spans="1:12" ht="15">
       <c r="A517" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="D517" s="2">
         <v>202301</v>
@@ -26823,13 +26826,13 @@
     </row>
     <row r="518" spans="1:12" ht="15">
       <c r="A518" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="D518" s="2">
         <v>202301</v>
@@ -26861,13 +26864,13 @@
     </row>
     <row r="519" spans="1:12" ht="15">
       <c r="A519" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="D519" s="2">
         <v>202301</v>
@@ -26899,13 +26902,13 @@
     </row>
     <row r="520" spans="1:12" ht="15">
       <c r="A520" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="D520" s="2">
         <v>202301</v>
@@ -26937,13 +26940,13 @@
     </row>
     <row r="521" spans="1:12" ht="15">
       <c r="A521" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="D521" s="2">
         <v>202301</v>
@@ -26975,13 +26978,13 @@
     </row>
     <row r="522" spans="1:12" ht="15">
       <c r="A522" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="D522" s="2">
         <v>202301</v>
@@ -27013,13 +27016,13 @@
     </row>
     <row r="523" spans="1:12" ht="15">
       <c r="A523" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="D523" s="2">
         <v>202301</v>
@@ -27051,13 +27054,13 @@
     </row>
     <row r="524" spans="1:12" ht="15">
       <c r="A524" s="8" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="D524" s="2">
         <v>202301</v>
@@ -27089,13 +27092,13 @@
     </row>
     <row r="525" spans="1:12" ht="15">
       <c r="A525" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="D525" s="2">
         <v>202301</v>
@@ -27127,13 +27130,13 @@
     </row>
     <row r="526" spans="1:12" ht="15">
       <c r="A526" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D526" s="2">
         <v>202301</v>
@@ -27165,13 +27168,13 @@
     </row>
     <row r="527" spans="1:12" ht="15">
       <c r="A527" s="8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="D527" s="2">
         <v>202301</v>
@@ -27203,13 +27206,13 @@
     </row>
     <row r="528" spans="1:12" ht="15">
       <c r="A528" s="8" t="s">
-        <v>342</v>
+        <v>810</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>343</v>
+        <v>1316</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>344</v>
+        <v>1813</v>
       </c>
       <c r="D528" s="2">
         <v>202301</v>
@@ -27241,13 +27244,13 @@
     </row>
     <row r="529" spans="1:12" ht="15">
       <c r="A529" s="8" t="s">
-        <v>811</v>
+        <v>342</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1317</v>
+        <v>343</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1814</v>
+        <v>344</v>
       </c>
       <c r="D529" s="2">
         <v>202301</v>
@@ -27279,13 +27282,13 @@
     </row>
     <row r="530" spans="1:12" ht="15">
       <c r="A530" s="8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="D530" s="2">
         <v>202301</v>
@@ -27317,13 +27320,13 @@
     </row>
     <row r="531" spans="1:12" ht="15">
       <c r="A531" s="8" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="D531" s="2">
         <v>202301</v>
@@ -27355,13 +27358,13 @@
     </row>
     <row r="532" spans="1:12" ht="15">
       <c r="A532" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D532" s="2">
         <v>202301</v>
@@ -27393,13 +27396,13 @@
     </row>
     <row r="533" spans="1:12" ht="15">
       <c r="A533" s="8" t="s">
-        <v>345</v>
+        <v>814</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>390</v>
+        <v>1320</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>346</v>
+        <v>1817</v>
       </c>
       <c r="D533" s="2">
         <v>202301</v>
@@ -27431,13 +27434,13 @@
     </row>
     <row r="534" spans="1:12" ht="15">
       <c r="A534" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D534" s="2">
         <v>202301</v>
@@ -27469,13 +27472,13 @@
     </row>
     <row r="535" spans="1:12" ht="15">
       <c r="A535" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D535" s="2">
         <v>202301</v>
@@ -27507,13 +27510,13 @@
     </row>
     <row r="536" spans="1:12" ht="15">
       <c r="A536" s="8" t="s">
-        <v>815</v>
+        <v>349</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1321</v>
+        <v>396</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1818</v>
+        <v>350</v>
       </c>
       <c r="D536" s="2">
         <v>202301</v>
@@ -27545,13 +27548,13 @@
     </row>
     <row r="537" spans="1:12" ht="15">
       <c r="A537" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="D537" s="2">
         <v>202301</v>
@@ -27583,13 +27586,13 @@
     </row>
     <row r="538" spans="1:12" ht="15">
       <c r="A538" s="8" t="s">
-        <v>351</v>
+        <v>816</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>352</v>
+        <v>1322</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>353</v>
+        <v>1819</v>
       </c>
       <c r="D538" s="2">
         <v>202301</v>
@@ -27621,13 +27624,13 @@
     </row>
     <row r="539" spans="1:12" ht="15">
       <c r="A539" s="8" t="s">
-        <v>817</v>
+        <v>351</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1323</v>
+        <v>352</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1820</v>
+        <v>353</v>
       </c>
       <c r="D539" s="2">
         <v>202301</v>
@@ -27659,13 +27662,13 @@
     </row>
     <row r="540" spans="1:12" ht="15">
       <c r="A540" s="8" t="s">
-        <v>354</v>
+        <v>817</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>355</v>
+        <v>1323</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>356</v>
+        <v>1820</v>
       </c>
       <c r="D540" s="2">
         <v>202301</v>
@@ -27697,13 +27700,13 @@
     </row>
     <row r="541" spans="1:12" ht="15">
       <c r="A541" s="8" t="s">
-        <v>818</v>
+        <v>354</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1324</v>
+        <v>355</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1821</v>
+        <v>356</v>
       </c>
       <c r="D541" s="2">
         <v>202301</v>
@@ -27735,13 +27738,13 @@
     </row>
     <row r="542" spans="1:12" ht="15">
       <c r="A542" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="D542" s="2">
         <v>202301</v>
@@ -27773,13 +27776,13 @@
     </row>
     <row r="543" spans="1:12" ht="15">
       <c r="A543" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="D543" s="2">
         <v>202301</v>
@@ -27811,13 +27814,13 @@
     </row>
     <row r="544" spans="1:12" ht="15">
       <c r="A544" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="D544" s="2">
         <v>202301</v>
@@ -27849,13 +27852,13 @@
     </row>
     <row r="545" spans="1:12" ht="15">
       <c r="A545" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="D545" s="2">
         <v>202301</v>
@@ -27887,13 +27890,13 @@
     </row>
     <row r="546" spans="1:12" ht="15">
       <c r="A546" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="D546" s="2">
         <v>202301</v>
@@ -27925,13 +27928,13 @@
     </row>
     <row r="547" spans="1:12" ht="15">
       <c r="A547" s="8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="D547" s="2">
         <v>202301</v>
@@ -27963,13 +27966,13 @@
     </row>
     <row r="548" spans="1:12" ht="15">
       <c r="A548" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="D548" s="2">
         <v>202301</v>
@@ -28001,13 +28004,13 @@
     </row>
     <row r="549" spans="1:12" ht="15">
       <c r="A549" s="8" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="D549" s="2">
         <v>202301</v>
@@ -28039,13 +28042,13 @@
     </row>
     <row r="550" spans="1:12" ht="15">
       <c r="A550" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="D550" s="2">
         <v>202301</v>
@@ -28077,13 +28080,13 @@
     </row>
     <row r="551" spans="1:12" ht="15">
       <c r="A551" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="D551" s="2">
         <v>202301</v>
@@ -28115,13 +28118,13 @@
     </row>
     <row r="552" spans="1:12" ht="15">
       <c r="A552" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="D552" s="2">
         <v>202301</v>
@@ -28153,13 +28156,13 @@
     </row>
     <row r="553" spans="1:12" ht="15">
       <c r="A553" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="D553" s="2">
         <v>202301</v>
@@ -28191,13 +28194,13 @@
     </row>
     <row r="554" spans="1:12" ht="15">
       <c r="A554" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="D554" s="2">
         <v>202301</v>
@@ -28229,13 +28232,13 @@
     </row>
     <row r="555" spans="1:12" ht="15">
       <c r="A555" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="D555" s="2">
         <v>202301</v>
@@ -28267,13 +28270,13 @@
     </row>
     <row r="556" spans="1:12" ht="15">
       <c r="A556" s="8" t="s">
-        <v>357</v>
+        <v>832</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>358</v>
+        <v>1338</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>359</v>
+        <v>1835</v>
       </c>
       <c r="D556" s="2">
         <v>202301</v>
@@ -28305,13 +28308,13 @@
     </row>
     <row r="557" spans="1:12" ht="15">
       <c r="A557" s="8" t="s">
-        <v>833</v>
+        <v>357</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1339</v>
+        <v>358</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1836</v>
+        <v>359</v>
       </c>
       <c r="D557" s="2">
         <v>202301</v>
@@ -28343,13 +28346,13 @@
     </row>
     <row r="558" spans="1:12" ht="15">
       <c r="A558" s="8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="D558" s="2">
         <v>202301</v>
@@ -28381,13 +28384,13 @@
     </row>
     <row r="559" spans="1:12" ht="15">
       <c r="A559" s="8" t="s">
-        <v>360</v>
+        <v>834</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>361</v>
+        <v>1340</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>362</v>
+        <v>1837</v>
       </c>
       <c r="D559" s="2">
         <v>202301</v>
@@ -28419,13 +28422,13 @@
     </row>
     <row r="560" spans="1:12" ht="15">
       <c r="A560" s="8" t="s">
-        <v>835</v>
+        <v>360</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1341</v>
+        <v>361</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1838</v>
+        <v>362</v>
       </c>
       <c r="D560" s="2">
         <v>202301</v>
@@ -28457,13 +28460,13 @@
     </row>
     <row r="561" spans="1:12" ht="15">
       <c r="A561" s="8" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="D561" s="2">
         <v>202301</v>
@@ -28495,13 +28498,13 @@
     </row>
     <row r="562" spans="1:12" ht="15">
       <c r="A562" s="8" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="D562" s="2">
         <v>202301</v>
@@ -28533,13 +28536,13 @@
     </row>
     <row r="563" spans="1:12" ht="15">
       <c r="A563" s="8" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="D563" s="2">
         <v>202301</v>
@@ -28571,13 +28574,13 @@
     </row>
     <row r="564" spans="1:12" ht="15">
       <c r="A564" s="8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="D564" s="2">
         <v>202301</v>
@@ -28609,13 +28612,13 @@
     </row>
     <row r="565" spans="1:12" ht="15">
       <c r="A565" s="8" t="s">
-        <v>363</v>
+        <v>839</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>364</v>
+        <v>1345</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>365</v>
+        <v>1842</v>
       </c>
       <c r="D565" s="2">
         <v>202301</v>
@@ -28647,13 +28650,13 @@
     </row>
     <row r="566" spans="1:12" ht="15">
       <c r="A566" s="8" t="s">
-        <v>840</v>
+        <v>363</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1843</v>
+        <v>365</v>
       </c>
       <c r="D566" s="2">
         <v>202301</v>
@@ -28685,13 +28688,13 @@
     </row>
     <row r="567" spans="1:12" ht="15">
       <c r="A567" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1346</v>
+        <v>343</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="D567" s="2">
         <v>202301</v>
@@ -28723,13 +28726,13 @@
     </row>
     <row r="568" spans="1:12" ht="15">
       <c r="A568" s="8" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="D568" s="2">
         <v>202301</v>
@@ -28761,13 +28764,13 @@
     </row>
     <row r="569" spans="1:12" ht="15">
       <c r="A569" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="D569" s="2">
         <v>202301</v>
@@ -28799,13 +28802,13 @@
     </row>
     <row r="570" spans="1:12" ht="15">
       <c r="A570" s="8" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="D570" s="2">
         <v>202301</v>
@@ -28837,13 +28840,13 @@
     </row>
     <row r="571" spans="1:12" ht="15">
       <c r="A571" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="D571" s="2">
         <v>202301</v>
@@ -28875,13 +28878,13 @@
     </row>
     <row r="572" spans="1:12" ht="15">
       <c r="A572" s="8" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="D572" s="2">
         <v>202301</v>
@@ -28913,13 +28916,13 @@
     </row>
     <row r="573" spans="1:12" ht="15">
       <c r="A573" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="D573" s="2">
         <v>202301</v>
@@ -28951,13 +28954,13 @@
     </row>
     <row r="574" spans="1:12" ht="15">
       <c r="A574" s="8" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="D574" s="2">
         <v>202301</v>
@@ -28989,13 +28992,13 @@
     </row>
     <row r="575" spans="1:12" ht="15">
       <c r="A575" s="8" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="D575" s="2">
         <v>202301</v>
@@ -29027,13 +29030,13 @@
     </row>
     <row r="576" spans="1:12" ht="15">
       <c r="A576" s="8" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="D576" s="2">
         <v>202301</v>
@@ -29065,13 +29068,13 @@
     </row>
     <row r="577" spans="1:12" ht="15">
       <c r="A577" s="8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="D577" s="2">
         <v>202301</v>
@@ -29103,13 +29106,13 @@
     </row>
     <row r="578" spans="1:12" ht="15">
       <c r="A578" s="8" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="D578" s="2">
         <v>202301</v>
@@ -29141,13 +29144,13 @@
     </row>
     <row r="579" spans="1:12" ht="15">
       <c r="A579" s="8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="D579" s="2">
         <v>202301</v>
@@ -29179,13 +29182,13 @@
     </row>
     <row r="580" spans="1:12" ht="15">
       <c r="A580" s="8" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="D580" s="2">
         <v>202301</v>
@@ -29217,13 +29220,13 @@
     </row>
     <row r="581" spans="1:12" ht="15">
       <c r="A581" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="D581" s="2">
         <v>202301</v>
@@ -29255,7 +29258,7 @@
     </row>
     <row r="582" spans="1:12" ht="15">
       <c r="A582" s="8" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>1360</v>
@@ -29293,13 +29296,13 @@
     </row>
     <row r="583" spans="1:12" ht="15">
       <c r="A583" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="D583" s="2">
         <v>202301</v>
@@ -29331,13 +29334,13 @@
     </row>
     <row r="584" spans="1:12" ht="15">
       <c r="A584" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="D584" s="2">
         <v>202301</v>
@@ -29369,13 +29372,13 @@
     </row>
     <row r="585" spans="1:12" ht="15">
       <c r="A585" s="8" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="D585" s="2">
         <v>202301</v>
@@ -29407,13 +29410,13 @@
     </row>
     <row r="586" spans="1:12" ht="15">
       <c r="A586" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="D586" s="2">
         <v>202301</v>
@@ -29445,13 +29448,13 @@
     </row>
     <row r="587" spans="1:12" ht="15">
       <c r="A587" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="D587" s="2">
         <v>202301</v>
@@ -29483,13 +29486,13 @@
     </row>
     <row r="588" spans="1:12" ht="15">
       <c r="A588" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="D588" s="2">
         <v>202301</v>
@@ -29521,13 +29524,13 @@
     </row>
     <row r="589" spans="1:12" ht="15">
       <c r="A589" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="D589" s="2">
         <v>202301</v>
@@ -29559,13 +29562,13 @@
     </row>
     <row r="590" spans="1:12" ht="15">
       <c r="A590" s="8" t="s">
-        <v>366</v>
+        <v>863</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>367</v>
+        <v>1367</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>368</v>
+        <v>1865</v>
       </c>
       <c r="D590" s="2">
         <v>202301</v>
@@ -29597,13 +29600,13 @@
     </row>
     <row r="591" spans="1:12" ht="15">
       <c r="A591" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D591" s="2">
         <v>202301</v>
@@ -29635,13 +29638,13 @@
     </row>
     <row r="592" spans="1:12" ht="15">
       <c r="A592" s="8" t="s">
-        <v>864</v>
+        <v>369</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1368</v>
+        <v>370</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1866</v>
+        <v>371</v>
       </c>
       <c r="D592" s="2">
         <v>202301</v>
@@ -29673,13 +29676,13 @@
     </row>
     <row r="593" spans="1:12" ht="15">
       <c r="A593" s="8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="D593" s="2">
         <v>202301</v>
@@ -29711,13 +29714,13 @@
     </row>
     <row r="594" spans="1:12" ht="15">
       <c r="A594" s="8" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="D594" s="2">
         <v>202301</v>
@@ -29749,13 +29752,13 @@
     </row>
     <row r="595" spans="1:12" ht="15">
       <c r="A595" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="D595" s="2">
         <v>202301</v>
@@ -29787,13 +29790,13 @@
     </row>
     <row r="596" spans="1:12" ht="15">
       <c r="A596" s="8" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="D596" s="2">
         <v>202301</v>
@@ -29825,13 +29828,13 @@
     </row>
     <row r="597" spans="1:12" ht="15">
       <c r="A597" s="8" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="D597" s="2">
         <v>202301</v>
@@ -29863,13 +29866,13 @@
     </row>
     <row r="598" spans="1:12" ht="15">
       <c r="A598" s="8" t="s">
-        <v>372</v>
+        <v>869</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>373</v>
+        <v>1372</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>374</v>
+        <v>1871</v>
       </c>
       <c r="D598" s="2">
         <v>202301</v>
@@ -29901,13 +29904,13 @@
     </row>
     <row r="599" spans="1:12" ht="15">
       <c r="A599" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>1373</v>
+        <v>373</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1872</v>
+        <v>374</v>
       </c>
       <c r="D599" s="2">
         <v>202301</v>
@@ -29939,13 +29942,13 @@
     </row>
     <row r="600" spans="1:12" ht="15">
       <c r="A600" s="8" t="s">
-        <v>870</v>
+        <v>375</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="D600" s="2">
         <v>202301</v>
@@ -29977,13 +29980,13 @@
     </row>
     <row r="601" spans="1:12" ht="15">
       <c r="A601" s="8" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="D601" s="2">
         <v>202301</v>
@@ -30015,13 +30018,13 @@
     </row>
     <row r="602" spans="1:12" ht="15">
       <c r="A602" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="D602" s="2">
         <v>202301</v>
@@ -30053,13 +30056,13 @@
     </row>
     <row r="603" spans="1:12" ht="15">
       <c r="A603" s="8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="D603" s="2">
         <v>202301</v>
@@ -30091,13 +30094,13 @@
     </row>
     <row r="604" spans="1:12" ht="15">
       <c r="A604" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="D604" s="2">
         <v>202301</v>
@@ -30129,13 +30132,13 @@
     </row>
     <row r="605" spans="1:12" ht="15">
       <c r="A605" s="8" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="D605" s="2">
         <v>202301</v>
@@ -30167,13 +30170,13 @@
     </row>
     <row r="606" spans="1:12" ht="15">
       <c r="A606" s="8" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="D606" s="2">
         <v>202301</v>
@@ -30205,13 +30208,13 @@
     </row>
     <row r="607" spans="1:12" ht="15">
       <c r="A607" s="8" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="D607" s="2">
         <v>202301</v>
@@ -30243,13 +30246,13 @@
     </row>
     <row r="608" spans="1:12" ht="15">
       <c r="A608" s="8" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="D608" s="2">
         <v>202301</v>
@@ -30281,13 +30284,13 @@
     </row>
     <row r="609" spans="1:12" ht="15">
       <c r="A609" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="D609" s="2">
         <v>202301</v>
@@ -30319,12 +30322,14 @@
     </row>
     <row r="610" spans="1:12" ht="15">
       <c r="A610" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1383</v>
-      </c>
-      <c r="C610"/>
+        <v>1382</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>1881</v>
+      </c>
       <c r="D610" s="2">
         <v>202301</v>
       </c>
@@ -30355,14 +30360,12 @@
     </row>
     <row r="611" spans="1:12" ht="15">
       <c r="A611" s="8" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C611" s="2" t="s">
-        <v>1882</v>
-      </c>
+        <v>1383</v>
+      </c>
+      <c r="C611"/>
       <c r="D611" s="2">
         <v>202301</v>
       </c>
@@ -30393,13 +30396,13 @@
     </row>
     <row r="612" spans="1:12" ht="15">
       <c r="A612" s="8" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="D612" s="2">
         <v>202301</v>
@@ -30431,13 +30434,13 @@
     </row>
     <row r="613" spans="1:12" ht="15">
       <c r="A613" s="8" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="D613" s="2">
         <v>202301</v>
@@ -30469,13 +30472,13 @@
     </row>
     <row r="614" spans="1:12" ht="15">
       <c r="A614" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="D614" s="2">
         <v>202301</v>
@@ -30507,13 +30510,13 @@
     </row>
     <row r="615" spans="1:12" ht="15">
       <c r="A615" s="8" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="D615" s="2">
         <v>202301</v>
@@ -30545,13 +30548,13 @@
     </row>
     <row r="616" spans="1:12" ht="15">
       <c r="A616" s="8" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="D616" s="2">
         <v>202301</v>
@@ -30583,13 +30586,13 @@
     </row>
     <row r="617" spans="1:12" ht="15">
       <c r="A617" s="8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="D617" s="2">
         <v>202301</v>
@@ -30621,13 +30624,13 @@
     </row>
     <row r="618" spans="1:12" ht="15">
       <c r="A618" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="D618" s="2">
         <v>202301</v>
@@ -30659,13 +30662,13 @@
     </row>
     <row r="619" spans="1:12" ht="15">
       <c r="A619" s="8" t="s">
-        <v>376</v>
+        <v>888</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>377</v>
+        <v>1391</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>378</v>
+        <v>1889</v>
       </c>
       <c r="D619" s="2">
         <v>202301</v>
@@ -30697,13 +30700,13 @@
     </row>
     <row r="620" spans="1:12" ht="15">
       <c r="A620" s="8" t="s">
-        <v>889</v>
+        <v>376</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1392</v>
+        <v>377</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>1890</v>
+        <v>378</v>
       </c>
       <c r="D620" s="2">
         <v>202301</v>
@@ -30735,13 +30738,13 @@
     </row>
     <row r="621" spans="1:12" ht="15">
       <c r="A621" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D621" s="2">
         <v>202301</v>
@@ -30773,13 +30776,13 @@
     </row>
     <row r="622" spans="1:12" ht="15">
       <c r="A622" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="D622" s="2">
         <v>202301</v>
@@ -30811,12 +30814,14 @@
     </row>
     <row r="623" spans="1:12" ht="15">
       <c r="A623" s="8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1395</v>
-      </c>
-      <c r="C623"/>
+        <v>1394</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>1892</v>
+      </c>
       <c r="D623" s="2">
         <v>202301</v>
       </c>
@@ -30847,14 +30852,12 @@
     </row>
     <row r="624" spans="1:12" ht="15">
       <c r="A624" s="8" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>1893</v>
-      </c>
+        <v>1395</v>
+      </c>
+      <c r="C624"/>
       <c r="D624" s="2">
         <v>202301</v>
       </c>
@@ -30885,13 +30888,13 @@
     </row>
     <row r="625" spans="1:12" ht="15">
       <c r="A625" s="8" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="D625" s="2">
         <v>202301</v>
@@ -30923,13 +30926,13 @@
     </row>
     <row r="626" spans="1:12" ht="15">
       <c r="A626" s="8" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>392</v>
+        <v>1397</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>380</v>
+        <v>1894</v>
       </c>
       <c r="D626" s="2">
         <v>202301</v>
@@ -30961,7 +30964,7 @@
     </row>
     <row r="627" spans="1:12" ht="15">
       <c r="A627" s="8" t="s">
-        <v>379</v>
+        <v>895</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>392</v>
@@ -30999,13 +31002,13 @@
     </row>
     <row r="628" spans="1:12" ht="15">
       <c r="A628" s="8" t="s">
-        <v>896</v>
+        <v>379</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1398</v>
+        <v>392</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1895</v>
+        <v>380</v>
       </c>
       <c r="D628" s="2">
         <v>202301</v>
@@ -31037,13 +31040,13 @@
     </row>
     <row r="629" spans="1:12" ht="15">
       <c r="A629" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="D629" s="2">
         <v>202301</v>
@@ -31075,13 +31078,13 @@
     </row>
     <row r="630" spans="1:12" ht="15">
       <c r="A630" s="8" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="D630" s="2">
         <v>202301</v>
@@ -31113,13 +31116,13 @@
     </row>
     <row r="631" spans="1:12" ht="15">
       <c r="A631" s="8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="D631" s="2">
         <v>202301</v>
@@ -31151,13 +31154,13 @@
     </row>
     <row r="632" spans="1:12" ht="15">
       <c r="A632" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="D632" s="2">
         <v>202301</v>
@@ -31189,13 +31192,13 @@
     </row>
     <row r="633" spans="1:12" ht="15">
       <c r="A633" s="8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="D633" s="2">
         <v>202301</v>
@@ -31227,13 +31230,13 @@
     </row>
     <row r="634" spans="1:12" ht="15">
       <c r="A634" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="D634" s="2">
         <v>202301</v>
@@ -31265,13 +31268,13 @@
     </row>
     <row r="635" spans="1:12" ht="15">
       <c r="A635" s="8" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="D635" s="2">
         <v>202301</v>
@@ -31303,13 +31306,13 @@
     </row>
     <row r="636" spans="1:12" ht="15">
       <c r="A636" s="8" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="D636" s="2">
         <v>202301</v>
@@ -31341,13 +31344,13 @@
     </row>
     <row r="637" spans="1:12" ht="15">
       <c r="A637" s="8" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="D637" s="2">
         <v>202301</v>
@@ -31379,13 +31382,13 @@
     </row>
     <row r="638" spans="1:12" ht="15">
       <c r="A638" s="8" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="D638" s="2">
         <v>202301</v>
@@ -31417,13 +31420,13 @@
     </row>
     <row r="639" spans="1:12" ht="15">
       <c r="A639" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="D639" s="2">
         <v>202301</v>
@@ -31455,13 +31458,13 @@
     </row>
     <row r="640" spans="1:12" ht="15">
       <c r="A640" s="8" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="D640" s="2">
         <v>202301</v>
@@ -31493,13 +31496,13 @@
     </row>
     <row r="641" spans="1:12" ht="15">
       <c r="A641" s="8" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="D641" s="2">
         <v>202301</v>
@@ -31531,13 +31534,13 @@
     </row>
     <row r="642" spans="1:12" ht="15">
       <c r="A642" s="8" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="D642" s="2">
         <v>202301</v>
@@ -31569,13 +31572,13 @@
     </row>
     <row r="643" spans="1:12" ht="15">
       <c r="A643" s="8" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="D643" s="2">
         <v>202301</v>
@@ -31607,13 +31610,13 @@
     </row>
     <row r="644" spans="1:12" ht="15">
       <c r="A644" s="8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="D644" s="2">
         <v>202301</v>
@@ -31645,13 +31648,13 @@
     </row>
     <row r="645" spans="1:12" ht="15">
       <c r="A645" s="8" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="D645" s="2">
         <v>202301</v>
@@ -31683,13 +31686,13 @@
     </row>
     <row r="646" spans="1:12" ht="15">
       <c r="A646" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="D646" s="2">
         <v>202301</v>
@@ -31721,13 +31724,13 @@
     </row>
     <row r="647" spans="1:12" ht="15">
       <c r="A647" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="D647" s="2">
         <v>202301</v>
@@ -31759,13 +31762,13 @@
     </row>
     <row r="648" spans="1:12" ht="15">
       <c r="A648" s="8" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="D648" s="2">
         <v>202301</v>
@@ -31797,13 +31800,13 @@
     </row>
     <row r="649" spans="1:12" ht="15">
       <c r="A649" s="8" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D649" s="2">
         <v>202301</v>
@@ -31835,13 +31838,13 @@
     </row>
     <row r="650" spans="1:12" ht="15">
       <c r="A650" s="8" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D650" s="2">
         <v>202301</v>
@@ -31873,13 +31876,13 @@
     </row>
     <row r="651" spans="1:12" ht="15">
       <c r="A651" s="8" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="D651" s="2">
         <v>202301</v>
@@ -31911,13 +31914,13 @@
     </row>
     <row r="652" spans="1:12" ht="15">
       <c r="A652" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="D652" s="2">
         <v>202301</v>
@@ -31949,13 +31952,13 @@
     </row>
     <row r="653" spans="1:12" ht="15">
       <c r="A653" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D653" s="2">
         <v>202301</v>
@@ -31987,13 +31990,13 @@
     </row>
     <row r="654" spans="1:12" ht="15">
       <c r="A654" s="8" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D654" s="2">
         <v>202301</v>
@@ -32025,13 +32028,13 @@
     </row>
     <row r="655" spans="1:12" ht="15">
       <c r="A655" s="8" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="D655" s="2">
         <v>202301</v>
@@ -32063,13 +32066,13 @@
     </row>
     <row r="656" spans="1:12" ht="15">
       <c r="A656" s="8" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="D656" s="2">
         <v>202301</v>
@@ -32101,13 +32104,13 @@
     </row>
     <row r="657" spans="1:12" ht="15">
       <c r="A657" s="8" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D657" s="2">
         <v>202301</v>
@@ -32139,13 +32142,13 @@
     </row>
     <row r="658" spans="1:12" ht="15">
       <c r="A658" s="8" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D658" s="2">
         <v>202301</v>
@@ -32177,13 +32180,13 @@
     </row>
     <row r="659" spans="1:12" ht="15">
       <c r="A659" s="8" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="D659" s="2">
         <v>202301</v>
@@ -32215,13 +32218,13 @@
     </row>
     <row r="660" spans="1:12" ht="15">
       <c r="A660" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="D660" s="2">
         <v>202301</v>
@@ -32253,13 +32256,13 @@
     </row>
     <row r="661" spans="1:12" ht="15">
       <c r="A661" s="8" t="s">
-        <v>381</v>
+        <v>928</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>382</v>
+        <v>1430</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>383</v>
+        <v>1926</v>
       </c>
       <c r="D661" s="2">
         <v>202301</v>
@@ -32291,13 +32294,13 @@
     </row>
     <row r="662" spans="1:12" ht="15">
       <c r="A662" s="8" t="s">
-        <v>929</v>
+        <v>381</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1431</v>
+        <v>382</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1927</v>
+        <v>383</v>
       </c>
       <c r="D662" s="2">
         <v>202301</v>
@@ -32329,39 +32332,77 @@
     </row>
     <row r="663" spans="1:12" ht="15">
       <c r="A663" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C663" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D663" s="2">
+        <v>202301</v>
+      </c>
+      <c r="E663" s="5">
+        <v>0</v>
+      </c>
+      <c r="F663" s="5">
+        <v>0</v>
+      </c>
+      <c r="G663" s="5">
+        <v>0</v>
+      </c>
+      <c r="H663" s="5">
+        <v>0</v>
+      </c>
+      <c r="I663" s="5">
+        <v>0</v>
+      </c>
+      <c r="J663" s="5">
+        <v>0</v>
+      </c>
+      <c r="K663" s="5">
+        <v>0</v>
+      </c>
+      <c r="L663" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:12" ht="15">
+      <c r="A664" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="B663" s="2" t="s">
+      <c r="B664" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="C663" s="2" t="s">
+      <c r="C664" s="2" t="s">
         <v>1928</v>
       </c>
-      <c r="D663" s="2">
-        <v>202301</v>
-      </c>
-      <c r="E663" s="5">
-        <v>0</v>
-      </c>
-      <c r="F663" s="5">
-        <v>0</v>
-      </c>
-      <c r="G663" s="5">
-        <v>0</v>
-      </c>
-      <c r="H663" s="5">
-        <v>0</v>
-      </c>
-      <c r="I663" s="5">
-        <v>0</v>
-      </c>
-      <c r="J663" s="5">
-        <v>0</v>
-      </c>
-      <c r="K663" s="5">
-        <v>0</v>
-      </c>
-      <c r="L663" s="5">
+      <c r="D664" s="2">
+        <v>202301</v>
+      </c>
+      <c r="E664" s="5">
+        <v>0</v>
+      </c>
+      <c r="F664" s="5">
+        <v>0</v>
+      </c>
+      <c r="G664" s="5">
+        <v>0</v>
+      </c>
+      <c r="H664" s="5">
+        <v>0</v>
+      </c>
+      <c r="I664" s="5">
+        <v>0</v>
+      </c>
+      <c r="J664" s="5">
+        <v>0</v>
+      </c>
+      <c r="K664" s="5">
+        <v>0</v>
+      </c>
+      <c r="L664" s="5">
         <v>0</v>
       </c>
     </row>

--- a/templates/Trial Balance_template.xlsx
+++ b/templates/Trial Balance_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardpalenik/Dropbox/python-development/GenAI/ecos/trial_balance/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55172CB2-1A30-AE4C-AC52-11152B0A5557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB69C62-C1F7-BD48-8D80-9896ED283EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial Balance_30.11.2025" sheetId="1" r:id="rId1"/>
